--- a/опт и Краснодар/2025/04,25/14,04,25 ПОКОМ КИ Новороссийск/дв 14,04,25 нррсч пок ки от Химича.xlsx
+++ b/опт и Краснодар/2025/04,25/14,04,25 ПОКОМ КИ Новороссийск/дв 14,04,25 нррсч пок ки от Химича.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\ПОКОМ\pokom_data\опт и Краснодар\2025\04,25\14,04,25 ПОКОМ КИ Новороссийск\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A2C02E-AA5E-4D59-AD63-3FB8F045C651}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73EB6250-61B3-4B42-9500-8A5398DF3528}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3147,7 +3147,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="4">
-        <f t="shared" ref="J5:R5" si="0">SUM(J6:J494)</f>
+        <f t="shared" ref="J5:S5" si="0">SUM(J6:J494)</f>
         <v>7030.5849999999991</v>
       </c>
       <c r="K5" s="4">
